--- a/config/gold-and-gears-generated/templates/GoldAndGearsEvidence.xlsx
+++ b/config/gold-and-gears-generated/templates/GoldAndGearsEvidence.xlsx
@@ -11,16 +11,17 @@
     <sheet name="SourceRecord" sheetId="2" r:id="rId2"/>
     <sheet name="Coverage" sheetId="3" r:id="rId3"/>
     <sheet name="ResearchGap" sheetId="4" r:id="rId4"/>
-    <sheet name="ReviewFixture" sheetId="5" r:id="rId5"/>
-    <sheet name="Manifest" sheetId="6" r:id="rId6"/>
-    <sheet name="PackIndex" sheetId="7" r:id="rId7"/>
+    <sheet name="ResearchGapAffected" sheetId="5" r:id="rId5"/>
+    <sheet name="ReviewFixture" sheetId="6" r:id="rId6"/>
+    <sheet name="Manifest" sheetId="7" r:id="rId7"/>
+    <sheet name="PackIndex" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="136">
   <si>
     <t>@table</t>
   </si>
@@ -292,7 +293,7 @@
     <t>GoldGearsResearchGap</t>
   </si>
   <si>
-    <t>9b2c9d0a11054e42</t>
+    <t>5b1ec839b492f83d</t>
   </si>
   <si>
     <t>gap_state</t>
@@ -304,7 +305,25 @@
     <t>policy_source_id</t>
   </si>
   <si>
-    <t>affected_records_json</t>
+    <t>GoldGearsResearchGapAffectedRecord</t>
+  </si>
+  <si>
+    <t>1f5e06bb8b0ecaa9</t>
+  </si>
+  <si>
+    <t>research_gap_id</t>
+  </si>
+  <si>
+    <t>ordinal</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>record_stable_key</t>
+  </si>
+  <si>
+    <t>ref&lt;GoldGearsResearchGap.id&gt;</t>
   </si>
   <si>
     <t>GoldGearsReviewFixture</t>
@@ -2119,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2133,12 +2152,11 @@
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
     <col min="15" max="16" width="12.7109375" style="5" customWidth="1"/>
     <col min="17" max="17" width="16.7109375" style="5" customWidth="1"/>
-    <col min="18" max="18" width="21.7109375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="5" customWidth="1"/>
-    <col min="20" max="20" width="21.7109375" style="5" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" style="5" customWidth="1"/>
+    <col min="19" max="19" width="21.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2170,7 +2188,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="24" customHeight="1">
+    <row r="2" spans="1:19" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -2223,16 +2241,13 @@
         <v>93</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="T2" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:19">
       <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
@@ -2285,16 +2300,13 @@
         <v>93</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="T3" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
@@ -2352,11 +2364,8 @@
       <c r="S4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="T4" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>49</v>
       </c>
@@ -2414,11 +2423,8 @@
       <c r="S5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="T5" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
         <v>50</v>
       </c>
@@ -2463,16 +2469,13 @@
         <v>52</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="T6" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="42" customHeight="1">
+    </row>
+    <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>61</v>
       </c>
@@ -2494,7 +2497,6 @@
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -2520,6 +2522,173 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="5" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="42" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="B8:B1007">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 0 to 2147483647." sqref="D8:D1007">
+      <formula1>0</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:X7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2550,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2574,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="24" customHeight="1">
@@ -2624,25 +2793,25 @@
         <v>23</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="W2" s="3" t="s">
         <v>73</v>
@@ -2698,25 +2867,25 @@
         <v>23</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="W3" s="5" t="s">
         <v>73</v>
@@ -2914,7 +3083,7 @@
         <v>58</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>59</v>
@@ -2929,7 +3098,7 @@
         <v>59</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
@@ -2986,7 +3155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3018,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3042,7 +3211,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="24" customHeight="1">
@@ -3059,58 +3228,58 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>86</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -3127,58 +3296,58 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>86</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -3322,7 +3491,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>52</v>
@@ -3451,7 +3620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3467,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3491,7 +3660,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -3508,10 +3677,10 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3528,10 +3697,10 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3579,7 +3748,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>52</v>
